--- a/models/parameterisations.xlsx
+++ b/models/parameterisations.xlsx
@@ -14599,9 +14599,21 @@
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>PBPKO:04057</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>volume fraction of blood</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04057</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
@@ -15296,9 +15308,21 @@
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>PBPKO:04090</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>fraction of gut intestinal tract</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04090</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
@@ -15504,9 +15528,21 @@
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>PBPKO:04058</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>volume fraction of red blood cells</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04058</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
@@ -18017,12 +18053,36 @@
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
-      <c r="O334" t="inlineStr"/>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18058,12 +18118,36 @@
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
-      <c r="O335" t="inlineStr"/>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>PBPKO:03004</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03004</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -18101,12 +18185,36 @@
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
-      <c r="O336" t="inlineStr"/>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18209,12 +18317,36 @@
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
-      <c r="O338" t="inlineStr"/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19548,9 +19680,21 @@
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>PBPKO:04057</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>volume fraction of blood</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04057</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
@@ -19867,12 +20011,36 @@
         </is>
       </c>
       <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr"/>
-      <c r="O364" t="inlineStr"/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>CHEBI:76967</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>human xenobiotic metabolite</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_76967</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19914,36 +20082,12 @@
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>PBPKO:00214</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>Michaelis constant  liver</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/PBPKO_00214</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>CHEBI:33216</t>
-        </is>
-      </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>bisphenol A</t>
-        </is>
-      </c>
-      <c r="O365" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
-        </is>
-      </c>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -20198,9 +20342,21 @@
         </is>
       </c>
       <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>PBPKO:04055</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>fraction of bile in liver</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04055</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr"/>
@@ -20245,12 +20401,36 @@
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
-      <c r="M370" t="inlineStr"/>
-      <c r="N370" t="inlineStr"/>
-      <c r="O370" t="inlineStr"/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>PBPKO:03020</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>intrinsic enterohepatic recirculation rate constant</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03020</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>CHEBI:76967</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>human xenobiotic metabolite</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_76967</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -20540,9 +20720,21 @@
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
-      <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>PBPKO:04043</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>enterocyte volume</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04043</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr"/>
@@ -20788,12 +20980,36 @@
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
-      <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr"/>
-      <c r="O379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20835,12 +21051,36 @@
         </is>
       </c>
       <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
-      <c r="M380" t="inlineStr"/>
-      <c r="N380" t="inlineStr"/>
-      <c r="O380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20882,12 +21122,36 @@
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
-      <c r="M381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
-      <c r="O381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -21071,12 +21335,36 @@
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
-      <c r="M384" t="inlineStr"/>
-      <c r="N384" t="inlineStr"/>
-      <c r="O384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -21118,12 +21406,36 @@
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
-      <c r="M385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
-      <c r="O385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -21165,12 +21477,36 @@
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
-      <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
-      <c r="M386" t="inlineStr"/>
-      <c r="N386" t="inlineStr"/>
-      <c r="O386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>PBPKO:03020</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>intrinsic enterohepatic recirculation rate constant</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03020</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -21212,12 +21548,36 @@
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
-      <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
-      <c r="M387" t="inlineStr"/>
-      <c r="N387" t="inlineStr"/>
-      <c r="O387" t="inlineStr"/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -21259,12 +21619,36 @@
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
-      <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
-      <c r="M388" t="inlineStr"/>
-      <c r="N388" t="inlineStr"/>
-      <c r="O388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -21306,12 +21690,36 @@
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
-      <c r="M389" t="inlineStr"/>
-      <c r="N389" t="inlineStr"/>
-      <c r="O389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>PBPKO:03054</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>cell fraction of intracellular water</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03054</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>CHEBI:76967</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>human xenobiotic metabolite</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_76967</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -21353,12 +21761,36 @@
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
-      <c r="O390" t="inlineStr"/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>PBPKO:03054</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>cell fraction of intracellular water</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03054</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21778,12 +22210,36 @@
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
-      <c r="O397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>PBPKO:03055</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>cell fraction of mitochondria</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03055</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>CHEBI:76967</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>human xenobiotic metabolite</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_76967</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21825,12 +22281,36 @@
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
-      <c r="M398" t="inlineStr"/>
-      <c r="N398" t="inlineStr"/>
-      <c r="O398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>PBPKO:03055</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>cell fraction of mitochondria</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03055</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -22604,9 +23084,21 @@
         </is>
       </c>
       <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>PBPKO:04058</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>volume fraction of red blood cells</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04058</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr"/>
       <c r="O411" t="inlineStr"/>
@@ -22718,12 +23210,36 @@
       </c>
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
-      <c r="O413" t="inlineStr"/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22761,12 +23277,36 @@
       </c>
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
-      <c r="O414" t="inlineStr"/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22804,12 +23344,36 @@
       </c>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
-      <c r="O415" t="inlineStr"/>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -23588,9 +24152,21 @@
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>PBPKO:04043</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>enterocyte volume</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04043</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr"/>
       <c r="O427" t="inlineStr"/>
@@ -23836,12 +24412,36 @@
         </is>
       </c>
       <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
-      <c r="M431" t="inlineStr"/>
-      <c r="N431" t="inlineStr"/>
-      <c r="O431" t="inlineStr"/>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -23883,12 +24483,36 @@
         </is>
       </c>
       <c r="I432" t="inlineStr"/>
-      <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
-      <c r="M432" t="inlineStr"/>
-      <c r="N432" t="inlineStr"/>
-      <c r="O432" t="inlineStr"/>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -23930,12 +24554,36 @@
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
-      <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
-      <c r="M433" t="inlineStr"/>
-      <c r="N433" t="inlineStr"/>
-      <c r="O433" t="inlineStr"/>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -24119,12 +24767,36 @@
         </is>
       </c>
       <c r="I436" t="inlineStr"/>
-      <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
-      <c r="M436" t="inlineStr"/>
-      <c r="N436" t="inlineStr"/>
-      <c r="O436" t="inlineStr"/>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -24166,12 +24838,36 @@
         </is>
       </c>
       <c r="I437" t="inlineStr"/>
-      <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr"/>
-      <c r="L437" t="inlineStr"/>
-      <c r="M437" t="inlineStr"/>
-      <c r="N437" t="inlineStr"/>
-      <c r="O437" t="inlineStr"/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -24213,12 +24909,36 @@
         </is>
       </c>
       <c r="I438" t="inlineStr"/>
-      <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr"/>
-      <c r="N438" t="inlineStr"/>
-      <c r="O438" t="inlineStr"/>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>PBPKO:03020</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>intrinsic enterohepatic recirculation rate constant</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03020</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -24260,12 +24980,36 @@
         </is>
       </c>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
-      <c r="K439" t="inlineStr"/>
-      <c r="L439" t="inlineStr"/>
-      <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr"/>
-      <c r="O439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -24307,12 +25051,36 @@
         </is>
       </c>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
-      <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr"/>
-      <c r="O440" t="inlineStr"/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -24354,9 +25122,21 @@
         </is>
       </c>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>PBPKO:04054</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>fraction of bile in small intestine</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04054</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr"/>
       <c r="N441" t="inlineStr"/>
       <c r="O441" t="inlineStr"/>
@@ -24401,9 +25181,21 @@
         </is>
       </c>
       <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>PBPKO:04054</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>fraction of bile in small intestine</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04054</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr"/>
       <c r="N442" t="inlineStr"/>
       <c r="O442" t="inlineStr"/>
@@ -24826,9 +25618,21 @@
         </is>
       </c>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>PBPKO:04055</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>fraction of bile in liver</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04055</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr"/>
       <c r="N449" t="inlineStr"/>
       <c r="O449" t="inlineStr"/>
@@ -24873,9 +25677,21 @@
         </is>
       </c>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>PBPKO:04055</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>fraction of bile in liver</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04055</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr"/>
       <c r="N450" t="inlineStr"/>
       <c r="O450" t="inlineStr"/>
@@ -25475,9 +26291,21 @@
         </is>
       </c>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>PBPKO:04043</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>enterocyte volume</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04043</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr"/>
       <c r="N460" t="inlineStr"/>
       <c r="O460" t="inlineStr"/>
@@ -25723,12 +26551,36 @@
         </is>
       </c>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr"/>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="inlineStr"/>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -25770,12 +26622,36 @@
         </is>
       </c>
       <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
-      <c r="K465" t="inlineStr"/>
-      <c r="L465" t="inlineStr"/>
-      <c r="M465" t="inlineStr"/>
-      <c r="N465" t="inlineStr"/>
-      <c r="O465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -25817,12 +26693,36 @@
         </is>
       </c>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr"/>
-      <c r="L466" t="inlineStr"/>
-      <c r="M466" t="inlineStr"/>
-      <c r="N466" t="inlineStr"/>
-      <c r="O466" t="inlineStr"/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -26006,12 +26906,36 @@
         </is>
       </c>
       <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
-      <c r="K469" t="inlineStr"/>
-      <c r="L469" t="inlineStr"/>
-      <c r="M469" t="inlineStr"/>
-      <c r="N469" t="inlineStr"/>
-      <c r="O469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -26053,12 +26977,36 @@
         </is>
       </c>
       <c r="I470" t="inlineStr"/>
-      <c r="J470" t="inlineStr"/>
-      <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
-      <c r="M470" t="inlineStr"/>
-      <c r="N470" t="inlineStr"/>
-      <c r="O470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>PBPKO:03018</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate of metabilite</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03018</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -26100,12 +27048,36 @@
         </is>
       </c>
       <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr"/>
-      <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
-      <c r="M471" t="inlineStr"/>
-      <c r="N471" t="inlineStr"/>
-      <c r="O471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>PBPKO:03020</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>intrinsic enterohepatic recirculation rate constant</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03020</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>CHEBI:33216</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>bisphenol A</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_33216</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -26147,12 +27119,36 @@
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
-      <c r="M472" t="inlineStr"/>
-      <c r="N472" t="inlineStr"/>
-      <c r="O472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>CHEBI:235438</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>bisphenol A beta-D-glucuronide</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_235438</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -26194,12 +27190,36 @@
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
-      <c r="M473" t="inlineStr"/>
-      <c r="N473" t="inlineStr"/>
-      <c r="O473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>PBPKO:03023</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>intrinsic reabsorption rate constant</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03023</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>CHEBI:167305</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>bisphenol A sulfate</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_167305</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -26241,9 +27261,21 @@
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>PBPKO:04054</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>fraction of bile in small intestine</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04054</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr"/>
       <c r="N474" t="inlineStr"/>
       <c r="O474" t="inlineStr"/>
@@ -26288,9 +27320,21 @@
         </is>
       </c>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>PBPKO:04054</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>fraction of bile in small intestine</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04054</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr"/>
       <c r="N475" t="inlineStr"/>
       <c r="O475" t="inlineStr"/>
@@ -26713,9 +27757,21 @@
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>PBPKO:04055</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>fraction of bile in liver</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04055</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr"/>
       <c r="N482" t="inlineStr"/>
       <c r="O482" t="inlineStr"/>
@@ -26760,9 +27816,21 @@
         </is>
       </c>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
-      <c r="L483" t="inlineStr"/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>PBPKO:04055</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>fraction of bile in liver</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_04055</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr"/>
       <c r="N483" t="inlineStr"/>
       <c r="O483" t="inlineStr"/>

--- a/models/parameterisations.xlsx
+++ b/models/parameterisations.xlsx
@@ -58652,12 +58652,36 @@
       </c>
       <c r="H1049" t="inlineStr"/>
       <c r="I1049" t="inlineStr"/>
-      <c r="J1049" t="inlineStr"/>
-      <c r="K1049" t="inlineStr"/>
-      <c r="L1049" t="inlineStr"/>
-      <c r="M1049" t="inlineStr"/>
-      <c r="N1049" t="inlineStr"/>
-      <c r="O1049" t="inlineStr"/>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M1049" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1049" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -58695,12 +58719,36 @@
       </c>
       <c r="H1050" t="inlineStr"/>
       <c r="I1050" t="inlineStr"/>
-      <c r="J1050" t="inlineStr"/>
-      <c r="K1050" t="inlineStr"/>
-      <c r="L1050" t="inlineStr"/>
-      <c r="M1050" t="inlineStr"/>
-      <c r="N1050" t="inlineStr"/>
-      <c r="O1050" t="inlineStr"/>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M1050" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1050" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -58738,12 +58786,36 @@
       </c>
       <c r="H1051" t="inlineStr"/>
       <c r="I1051" t="inlineStr"/>
-      <c r="J1051" t="inlineStr"/>
-      <c r="K1051" t="inlineStr"/>
-      <c r="L1051" t="inlineStr"/>
-      <c r="M1051" t="inlineStr"/>
-      <c r="N1051" t="inlineStr"/>
-      <c r="O1051" t="inlineStr"/>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M1051" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1051" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -58781,12 +58853,36 @@
       </c>
       <c r="H1052" t="inlineStr"/>
       <c r="I1052" t="inlineStr"/>
-      <c r="J1052" t="inlineStr"/>
-      <c r="K1052" t="inlineStr"/>
-      <c r="L1052" t="inlineStr"/>
-      <c r="M1052" t="inlineStr"/>
-      <c r="N1052" t="inlineStr"/>
-      <c r="O1052" t="inlineStr"/>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>PBPKO:03005</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>intrinsic fecal excretion rate</t>
+        </is>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03005</t>
+        </is>
+      </c>
+      <c r="M1052" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1052" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -58824,12 +58920,36 @@
       </c>
       <c r="H1053" t="inlineStr"/>
       <c r="I1053" t="inlineStr"/>
-      <c r="J1053" t="inlineStr"/>
-      <c r="K1053" t="inlineStr"/>
-      <c r="L1053" t="inlineStr"/>
-      <c r="M1053" t="inlineStr"/>
-      <c r="N1053" t="inlineStr"/>
-      <c r="O1053" t="inlineStr"/>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>PBPKO:03007</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>intrinsic biliary clearance rate</t>
+        </is>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03007</t>
+        </is>
+      </c>
+      <c r="M1053" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1053" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -59343,12 +59463,36 @@
       </c>
       <c r="H1062" t="inlineStr"/>
       <c r="I1062" t="inlineStr"/>
-      <c r="J1062" t="inlineStr"/>
-      <c r="K1062" t="inlineStr"/>
-      <c r="L1062" t="inlineStr"/>
-      <c r="M1062" t="inlineStr"/>
-      <c r="N1062" t="inlineStr"/>
-      <c r="O1062" t="inlineStr"/>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M1062" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1062" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -59386,12 +59530,36 @@
       </c>
       <c r="H1063" t="inlineStr"/>
       <c r="I1063" t="inlineStr"/>
-      <c r="J1063" t="inlineStr"/>
-      <c r="K1063" t="inlineStr"/>
-      <c r="L1063" t="inlineStr"/>
-      <c r="M1063" t="inlineStr"/>
-      <c r="N1063" t="inlineStr"/>
-      <c r="O1063" t="inlineStr"/>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M1063" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1063" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -59429,12 +59597,36 @@
       </c>
       <c r="H1064" t="inlineStr"/>
       <c r="I1064" t="inlineStr"/>
-      <c r="J1064" t="inlineStr"/>
-      <c r="K1064" t="inlineStr"/>
-      <c r="L1064" t="inlineStr"/>
-      <c r="M1064" t="inlineStr"/>
-      <c r="N1064" t="inlineStr"/>
-      <c r="O1064" t="inlineStr"/>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>PBPKO:03005</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>intrinsic fecal excretion rate</t>
+        </is>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03005</t>
+        </is>
+      </c>
+      <c r="M1064" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1064" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -59472,12 +59664,36 @@
       </c>
       <c r="H1065" t="inlineStr"/>
       <c r="I1065" t="inlineStr"/>
-      <c r="J1065" t="inlineStr"/>
-      <c r="K1065" t="inlineStr"/>
-      <c r="L1065" t="inlineStr"/>
-      <c r="M1065" t="inlineStr"/>
-      <c r="N1065" t="inlineStr"/>
-      <c r="O1065" t="inlineStr"/>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M1065" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1065" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -59515,12 +59731,36 @@
       </c>
       <c r="H1066" t="inlineStr"/>
       <c r="I1066" t="inlineStr"/>
-      <c r="J1066" t="inlineStr"/>
-      <c r="K1066" t="inlineStr"/>
-      <c r="L1066" t="inlineStr"/>
-      <c r="M1066" t="inlineStr"/>
-      <c r="N1066" t="inlineStr"/>
-      <c r="O1066" t="inlineStr"/>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>PBPKO:03007</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>intrinsic biliary clearance rate</t>
+        </is>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03007</t>
+        </is>
+      </c>
+      <c r="M1066" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1066" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -60144,12 +60384,36 @@
       </c>
       <c r="H1077" t="inlineStr"/>
       <c r="I1077" t="inlineStr"/>
-      <c r="J1077" t="inlineStr"/>
-      <c r="K1077" t="inlineStr"/>
-      <c r="L1077" t="inlineStr"/>
-      <c r="M1077" t="inlineStr"/>
-      <c r="N1077" t="inlineStr"/>
-      <c r="O1077" t="inlineStr"/>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>PBPKO:03005</t>
+        </is>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>intrinsic fecal excretion rate</t>
+        </is>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03005</t>
+        </is>
+      </c>
+      <c r="M1077" t="inlineStr">
+        <is>
+          <t>CHEBI:35549</t>
+        </is>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>perfluorooctanoic acid</t>
+        </is>
+      </c>
+      <c r="O1077" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_35549</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -60187,12 +60451,36 @@
       </c>
       <c r="H1078" t="inlineStr"/>
       <c r="I1078" t="inlineStr"/>
-      <c r="J1078" t="inlineStr"/>
-      <c r="K1078" t="inlineStr"/>
-      <c r="L1078" t="inlineStr"/>
-      <c r="M1078" t="inlineStr"/>
-      <c r="N1078" t="inlineStr"/>
-      <c r="O1078" t="inlineStr"/>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>PBPKO:03007</t>
+        </is>
+      </c>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>intrinsic biliary clearance rate</t>
+        </is>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03007</t>
+        </is>
+      </c>
+      <c r="M1078" t="inlineStr">
+        <is>
+          <t>CHEBI:35549</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>perfluorooctanoic acid</t>
+        </is>
+      </c>
+      <c r="O1078" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_35549</t>
+        </is>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -60723,17 +61011,17 @@
       </c>
       <c r="M1087" t="inlineStr">
         <is>
-          <t>CHEBI:35549</t>
+          <t>CHEBI:39421</t>
         </is>
       </c>
       <c r="N1087" t="inlineStr">
         <is>
-          <t>perfluorooctanoic acid</t>
+          <t>perfluorooctane-1-sulfonic acid</t>
         </is>
       </c>
       <c r="O1087" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/CHEBI_35549</t>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
         </is>
       </c>
     </row>
@@ -60773,12 +61061,36 @@
       </c>
       <c r="H1088" t="inlineStr"/>
       <c r="I1088" t="inlineStr"/>
-      <c r="J1088" t="inlineStr"/>
-      <c r="K1088" t="inlineStr"/>
-      <c r="L1088" t="inlineStr"/>
-      <c r="M1088" t="inlineStr"/>
-      <c r="N1088" t="inlineStr"/>
-      <c r="O1088" t="inlineStr"/>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>PBPKO:03001</t>
+        </is>
+      </c>
+      <c r="K1088" t="inlineStr">
+        <is>
+          <t>intrinsic gastric emptying rate</t>
+        </is>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03001</t>
+        </is>
+      </c>
+      <c r="M1088" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1088" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1088" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -60816,12 +61128,36 @@
       </c>
       <c r="H1089" t="inlineStr"/>
       <c r="I1089" t="inlineStr"/>
-      <c r="J1089" t="inlineStr"/>
-      <c r="K1089" t="inlineStr"/>
-      <c r="L1089" t="inlineStr"/>
-      <c r="M1089" t="inlineStr"/>
-      <c r="N1089" t="inlineStr"/>
-      <c r="O1089" t="inlineStr"/>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>PBPKO:03002</t>
+        </is>
+      </c>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>intrinsic absorption rate</t>
+        </is>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03002</t>
+        </is>
+      </c>
+      <c r="M1089" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1089" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
@@ -60859,12 +61195,36 @@
       </c>
       <c r="H1090" t="inlineStr"/>
       <c r="I1090" t="inlineStr"/>
-      <c r="J1090" t="inlineStr"/>
-      <c r="K1090" t="inlineStr"/>
-      <c r="L1090" t="inlineStr"/>
-      <c r="M1090" t="inlineStr"/>
-      <c r="N1090" t="inlineStr"/>
-      <c r="O1090" t="inlineStr"/>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>PBPKO:03005</t>
+        </is>
+      </c>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>intrinsic fecal excretion rate</t>
+        </is>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03005</t>
+        </is>
+      </c>
+      <c r="M1090" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1090" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1090" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -60902,12 +61262,36 @@
       </c>
       <c r="H1091" t="inlineStr"/>
       <c r="I1091" t="inlineStr"/>
-      <c r="J1091" t="inlineStr"/>
-      <c r="K1091" t="inlineStr"/>
-      <c r="L1091" t="inlineStr"/>
-      <c r="M1091" t="inlineStr"/>
-      <c r="N1091" t="inlineStr"/>
-      <c r="O1091" t="inlineStr"/>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>PBPKO:03003</t>
+        </is>
+      </c>
+      <c r="K1091" t="inlineStr">
+        <is>
+          <t>intrinsic stomach uptake rate</t>
+        </is>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03003</t>
+        </is>
+      </c>
+      <c r="M1091" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1091" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1091" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -60945,12 +61329,36 @@
       </c>
       <c r="H1092" t="inlineStr"/>
       <c r="I1092" t="inlineStr"/>
-      <c r="J1092" t="inlineStr"/>
-      <c r="K1092" t="inlineStr"/>
-      <c r="L1092" t="inlineStr"/>
-      <c r="M1092" t="inlineStr"/>
-      <c r="N1092" t="inlineStr"/>
-      <c r="O1092" t="inlineStr"/>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>PBPKO:03007</t>
+        </is>
+      </c>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>intrinsic biliary clearance rate</t>
+        </is>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/PBPKO_03007</t>
+        </is>
+      </c>
+      <c r="M1092" t="inlineStr">
+        <is>
+          <t>CHEBI:39421</t>
+        </is>
+      </c>
+      <c r="N1092" t="inlineStr">
+        <is>
+          <t>perfluorooctane-1-sulfonic acid</t>
+        </is>
+      </c>
+      <c r="O1092" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
+        </is>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -61005,17 +61413,17 @@
       </c>
       <c r="M1093" t="inlineStr">
         <is>
-          <t>CHEBI:35549</t>
+          <t>CHEBI:39421</t>
         </is>
       </c>
       <c r="N1093" t="inlineStr">
         <is>
-          <t>perfluorooctanoic acid</t>
+          <t>perfluorooctane-1-sulfonic acid</t>
         </is>
       </c>
       <c r="O1093" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/CHEBI_35549</t>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
         </is>
       </c>
     </row>
@@ -61072,17 +61480,17 @@
       </c>
       <c r="M1094" t="inlineStr">
         <is>
-          <t>CHEBI:35549</t>
+          <t>CHEBI:39421</t>
         </is>
       </c>
       <c r="N1094" t="inlineStr">
         <is>
-          <t>perfluorooctanoic acid</t>
+          <t>perfluorooctane-1-sulfonic acid</t>
         </is>
       </c>
       <c r="O1094" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/CHEBI_35549</t>
+          <t>http://purl.obolibrary.org/obo/CHEBI_39421</t>
         </is>
       </c>
     </row>
